--- a/astro-site/public/dl/kit-escandallos/11-dashboard-food-cost-mensual.xlsx
+++ b/astro-site/public/dl/kit-escandallos/11-dashboard-food-cost-mensual.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Dashboard'!$6:$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,9 +20,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt formatCode="#,##0 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
-    <numFmt formatCode="+0.0%;-0.0%" numFmtId="166"/>
+    <numFmt numFmtId="164" formatCode="#,##0 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -144,63 +146,63 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -273,14 +275,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -304,10 +305,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFD700"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -331,10 +332,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF4444"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -362,8 +363,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -389,8 +390,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -416,7 +417,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -431,9 +432,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -730,15 +731,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -760,6 +762,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -808,10 +811,19 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -819,29 +831,39 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="9" t="inlineStr">
         <is>
@@ -869,6 +891,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="12" t="inlineStr">
         <is>
@@ -915,15 +938,15 @@
       </c>
       <c r="E7" s="15">
         <f>IF(D7=0,"",C7/D7)</f>
-        <v/>
+        <v>0.30357142857142855</v>
       </c>
       <c r="F7" s="16">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G7" s="17">
         <f>IF(E7="","",E7-F7)</f>
-        <v/>
+        <v>0.0035714285714285587</v>
       </c>
     </row>
     <row r="8">
@@ -940,15 +963,15 @@
       </c>
       <c r="E8" s="19">
         <f>IF(D8=0,"",C8/D8)</f>
-        <v/>
+        <v>0.2943396226415094</v>
       </c>
       <c r="F8" s="20">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G8" s="21">
         <f>IF(E8="","",E8-F8)</f>
-        <v/>
+        <v>-0.005660377358490565</v>
       </c>
     </row>
     <row r="9">
@@ -965,15 +988,15 @@
       </c>
       <c r="E9" s="15">
         <f>IF(D9=0,"",C9/D9)</f>
-        <v/>
+        <v>0.30666666666666664</v>
       </c>
       <c r="F9" s="16">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G9" s="17">
         <f>IF(E9="","",E9-F9)</f>
-        <v/>
+        <v>0.006666666666666654</v>
       </c>
     </row>
     <row r="10">
@@ -990,7 +1013,7 @@
       </c>
       <c r="F10" s="20">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G10" s="21">
         <f>IF(E10="","",E10-F10)</f>
@@ -1011,7 +1034,7 @@
       </c>
       <c r="F11" s="16">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G11" s="17">
         <f>IF(E11="","",E11-F11)</f>
@@ -1032,7 +1055,7 @@
       </c>
       <c r="F12" s="20">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G12" s="21">
         <f>IF(E12="","",E12-F12)</f>
@@ -1053,7 +1076,7 @@
       </c>
       <c r="F13" s="16">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G13" s="17">
         <f>IF(E13="","",E13-F13)</f>
@@ -1074,7 +1097,7 @@
       </c>
       <c r="F14" s="20">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G14" s="21">
         <f>IF(E14="","",E14-F14)</f>
@@ -1095,7 +1118,7 @@
       </c>
       <c r="F15" s="16">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G15" s="17">
         <f>IF(E15="","",E15-F15)</f>
@@ -1116,7 +1139,7 @@
       </c>
       <c r="F16" s="20">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G16" s="21">
         <f>IF(E16="","",E16-F16)</f>
@@ -1137,7 +1160,7 @@
       </c>
       <c r="F17" s="16">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G17" s="17">
         <f>IF(E17="","",E17-F17)</f>
@@ -1158,7 +1181,7 @@
       </c>
       <c r="F18" s="20">
         <f>$C$4</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="G18" s="21">
         <f>IF(E18="","",E18-F18)</f>
@@ -1173,19 +1196,28 @@
       </c>
       <c r="C19" s="23">
         <f>SUM(C7:C18)</f>
-        <v/>
+        <v>25500.0</v>
       </c>
       <c r="D19" s="23">
         <f>SUM(D7:D18)</f>
-        <v/>
+        <v>84500.0</v>
       </c>
       <c r="E19" s="24">
         <f>IF(D19=0,"",C19/D19)</f>
-        <v/>
+        <v>0.30177514792899407</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-escandallos/11-dashboard-food-cost-mensual.xlsx
+++ b/astro-site/public/dl/kit-escandallos/11-dashboard-food-cost-mensual.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Dashboard'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Dashboard'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +84,30 @@
       <color rgb="00333333"/>
       <sz val="11"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00606060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -121,8 +144,33 @@
         <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -144,11 +192,31 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -198,10 +266,103 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="13" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="00FFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -276,6 +437,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -286,7 +448,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Food Cost Mensual vs Objetivo</a:t>
+              <a:t>Food Cost mensual vs objetivo</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -301,25 +463,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!E6</f>
+              <f>'Dashboard'!H6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFD700"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Dashboard'!$B$7:$B$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$7:$E$18</f>
+              <f>'Dashboard'!$H$7:$H$18</f>
             </numRef>
           </val>
         </ser>
@@ -328,25 +487,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!F6</f>
+              <f>'Dashboard'!I6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF4444"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Dashboard'!$B$7:$B$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$7:$F$18</f>
+              <f>'Dashboard'!$I$7:$I$18</f>
             </numRef>
           </val>
         </ser>
@@ -359,22 +515,8 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Mes</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -385,23 +527,10 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Porcentaje</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -425,7 +554,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9000000" cy="5040000"/>
+    <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -733,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -764,66 +893,154 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cómo usar esta plantilla</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>▸ Registra, mes a mes, el stock inicial, las compras, el stock final y las ventas. Sólo se escriben las celdas VERDES.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>▸ El food cost, la diferencia con tu objetivo, el estado y el gráfico salen solos.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>▸ Registra compras y ventas mensuales en la tabla</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>▸ El food cost % se calcula automáticamente</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>La fórmula (y por qué importa)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>▸ El gráfico se actualiza con los datos introducidos</t>
-        </is>
-      </c>
+      <c r="B10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>▸ Compara tu food cost real con el objetivo mes a mes</t>
+          <t>▸ Consumo = stock inicial + compras − stock final.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>▸ Food cost = consumo ÷ ventas.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>▸ NO es compras ÷ ventas. Una compra fuerte el día 28, o un vaciado de cámara, te movería el indicador varios puntos sin que hubiera cambiado nada en la cocina — que es justo el error que este dashboard existe para evitar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>▸ El stock en euros lo sacas de la pestaña «Inventario» del BONUS: cantidad × precio unitario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>IVA: todo en NETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>▸ Compras y ventas van SIN IVA. Si tu TPV te da las ventas con IVA incluido, divídelas entre 1,10 (o entre 1 + tu tipo) antes de escribirlas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>▸ Con las ventas en bruto el food cost sale unos 3 puntos mejor de lo real y te crees que vas bien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>▸ Columna «Estado»: VERDE («OK») si el food cost del mes está en el objetivo o por debajo; ROJO («ALERTA») si se pasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>▸ La columna «Food Cost %» se pinta de rojo cuando supera el objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>▸ El gráfico compara cada mes con el objetivo. Los meses sin datos no pintan barra: ni la real ni la del objetivo — sus celdas devuelven #N/A a propósito (es el único valor que el gráfico salta) y el formato condicional lo esconde de la tabla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>▸ La hoja está protegida SIN contraseña: sólo se escriben las celdas verdes. Revisar → Desproteger hoja para tocar el resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -851,365 +1068,623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="25" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="25" t="n"/>
+      <c r="H1" s="25" t="n"/>
+      <c r="I1" s="25" t="n"/>
+      <c r="J1" s="25" t="n"/>
+      <c r="K1" s="25" t="n"/>
+    </row>
     <row r="2">
-      <c r="B2" s="9" t="inlineStr">
+      <c r="A2" s="25" t="n"/>
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Dashboard Food Cost Mensual</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="25" t="n"/>
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Año:</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="29" t="n">
         <v>2026</v>
       </c>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Food Cost Objetivo (%):</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
+      <c r="A4" s="25" t="n"/>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Food Cost objetivo (%):</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="30" t="n">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="25" t="n"/>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Food cost = (stock inicial + compras − stock final) ÷ ventas. NO es compras ÷ ventas: una compra fuerte a fin de mes te movería el indicador varios puntos sin que hubiera cambiado nada en la cocina. Todo SIN IVA: si tu TPV te da las ventas con IVA, divídelas entre 1,10 antes de escribirlas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="25" t="n"/>
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Compras (€)</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Ventas (€)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Stock inicial (€)</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Compras netas sin IVA (€)</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Stock final (€)</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>Consumo (€)</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>Ventas netas sin IVA (€)</t>
+        </is>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>Food Cost %</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>Objetivo %</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="25" t="n"/>
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>8500</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>28000</v>
-      </c>
-      <c r="E7" s="15">
-        <f>IF(D7=0,"",C7/D7)</f>
-        <v>0.30357142857142855</v>
-      </c>
-      <c r="F7" s="16">
-        <f>$C$4</f>
+      <c r="C7" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F7" s="36">
+        <f>IFERROR(IF(G7=0,"",C7+D7-E7),"")</f>
+        <v>4800.0</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H7" s="37">
+        <f>IF(G7=0,NA(),F7/G7)</f>
         <v>0.3</v>
       </c>
-      <c r="G7" s="17">
-        <f>IF(E7="","",E7-F7)</f>
-        <v>0.0035714285714285587</v>
+      <c r="I7" s="38">
+        <f>IF(G7=0,NA(),$D$4)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J7" s="39">
+        <f>IFERROR(H7-I7,"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="40" t="str">
+        <f>IFERROR(IF(H7&lt;=$D$4,"OK","ALERTA"),"")</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>26500</v>
-      </c>
-      <c r="E8" s="19">
-        <f>IF(D8=0,"",C8/D8)</f>
-        <v>0.2943396226415094</v>
-      </c>
-      <c r="F8" s="20">
-        <f>$C$4</f>
+      <c r="C8" s="35" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F8" s="42">
+        <f>IFERROR(IF(G8=0,"",C8+D8-E8),"")</f>
+        <v>5500.0</v>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H8" s="43">
+        <f>IF(G8=0,NA(),F8/G8)</f>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="I8" s="44">
+        <f>IF(G8=0,NA(),$D$4)</f>
         <v>0.3</v>
       </c>
-      <c r="G8" s="21">
-        <f>IF(E8="","",E8-F8)</f>
-        <v>-0.005660377358490565</v>
+      <c r="J8" s="45">
+        <f>IFERROR(H8-I8,"")</f>
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="K8" s="46" t="str">
+        <f>IFERROR(IF(H8&lt;=$D$4,"OK","ALERTA"),"")</f>
+        <v>ALERTA</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="25" t="n"/>
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Marzo</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>9200</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E9" s="15">
-        <f>IF(D9=0,"",C9/D9)</f>
-        <v>0.30666666666666664</v>
-      </c>
-      <c r="F9" s="16">
-        <f>$C$4</f>
+      <c r="C9" s="35" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F9" s="36">
+        <f>IFERROR(IF(G9=0,"",C9+D9-E9),"")</f>
+        <v>5000.0</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>17000</v>
+      </c>
+      <c r="H9" s="37">
+        <f>IF(G9=0,NA(),F9/G9)</f>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="I9" s="38">
+        <f>IF(G9=0,NA(),$D$4)</f>
         <v>0.3</v>
       </c>
-      <c r="G9" s="17">
-        <f>IF(E9="","",E9-F9)</f>
-        <v>0.006666666666666654</v>
+      <c r="J9" s="39">
+        <f>IFERROR(H9-I9,"")</f>
+        <v>-0.00588235294117645</v>
+      </c>
+      <c r="K9" s="40" t="str">
+        <f>IFERROR(IF(H9&lt;=$D$4,"OK","ALERTA"),"")</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="19">
-        <f>IF(D10=0,"",C10/D10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G10" s="21">
-        <f>IF(E10="","",E10-F10)</f>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="42">
+        <f>IFERROR(IF(G10=0,"",C10+D10-E10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="43" t="str">
+        <f>IF(G10=0,NA(),F10/G10)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I10" s="44" t="str">
+        <f>IF(G10=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J10" s="45">
+        <f>IFERROR(H10-I10,"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="46">
+        <f>IFERROR(IF(H10&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="25" t="n"/>
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="15">
-        <f>IF(D11=0,"",C11/D11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G11" s="17">
-        <f>IF(E11="","",E11-F11)</f>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="36">
+        <f>IFERROR(IF(G11=0,"",C11+D11-E11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="37" t="str">
+        <f>IF(G11=0,NA(),F11/G11)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I11" s="38" t="str">
+        <f>IF(G11=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J11" s="39">
+        <f>IFERROR(H11-I11,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
+        <f>IFERROR(IF(H11&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="18" t="inlineStr">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="19">
-        <f>IF(D12=0,"",C12/D12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="20">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="21">
-        <f>IF(E12="","",E12-F12)</f>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="42">
+        <f>IFERROR(IF(G12=0,"",C12+D12-E12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="43" t="str">
+        <f>IF(G12=0,NA(),F12/G12)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I12" s="44" t="str">
+        <f>IF(G12=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J12" s="45">
+        <f>IFERROR(H12-I12,"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="46">
+        <f>IFERROR(IF(H12&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Julio</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="15">
-        <f>IF(D13=0,"",C13/D13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G13" s="17">
-        <f>IF(E13="","",E13-F13)</f>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="36">
+        <f>IFERROR(IF(G13=0,"",C13+D13-E13),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="37" t="str">
+        <f>IF(G13=0,NA(),F13/G13)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I13" s="38" t="str">
+        <f>IF(G13=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="39">
+        <f>IFERROR(H13-I13,"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="40">
+        <f>IFERROR(IF(H13&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="18" t="inlineStr">
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="19">
-        <f>IF(D14=0,"",C14/D14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="20">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G14" s="21">
-        <f>IF(E14="","",E14-F14)</f>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="42">
+        <f>IFERROR(IF(G14=0,"",C14+D14-E14),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="43" t="str">
+        <f>IF(G14=0,NA(),F14/G14)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" s="44" t="str">
+        <f>IF(G14=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" s="45">
+        <f>IFERROR(H14-I14,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="46">
+        <f>IFERROR(IF(H14&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="13" t="inlineStr">
+      <c r="A15" s="25" t="n"/>
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="15">
-        <f>IF(D15=0,"",C15/D15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G15" s="17">
-        <f>IF(E15="","",E15-F15)</f>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="36">
+        <f>IFERROR(IF(G15=0,"",C15+D15-E15),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="37" t="str">
+        <f>IF(G15=0,NA(),F15/G15)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I15" s="38" t="str">
+        <f>IF(G15=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="39">
+        <f>IFERROR(H15-I15,"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="40">
+        <f>IFERROR(IF(H15&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="18" t="inlineStr">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="19">
-        <f>IF(D16=0,"",C16/D16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="20">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G16" s="21">
-        <f>IF(E16="","",E16-F16)</f>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="42">
+        <f>IFERROR(IF(G16=0,"",C16+D16-E16),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="43" t="str">
+        <f>IF(G16=0,NA(),F16/G16)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" s="44" t="str">
+        <f>IF(G16=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J16" s="45">
+        <f>IFERROR(H16-I16,"")</f>
+        <v/>
+      </c>
+      <c r="K16" s="46">
+        <f>IFERROR(IF(H16&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="13" t="inlineStr">
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="15">
-        <f>IF(D17=0,"",C17/D17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G17" s="17">
-        <f>IF(E17="","",E17-F17)</f>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="36">
+        <f>IFERROR(IF(G17=0,"",C17+D17-E17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="37" t="str">
+        <f>IF(G17=0,NA(),F17/G17)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I17" s="38" t="str">
+        <f>IF(G17=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J17" s="39">
+        <f>IFERROR(H17-I17,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="40">
+        <f>IFERROR(IF(H17&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="19">
-        <f>IF(D18=0,"",C18/D18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="20">
-        <f>$C$4</f>
-        <v>0.3</v>
-      </c>
-      <c r="G18" s="21">
-        <f>IF(E18="","",E18-F18)</f>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="42">
+        <f>IFERROR(IF(G18=0,"",C18+D18-E18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="43" t="str">
+        <f>IF(G18=0,NA(),F18/G18)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" s="44" t="str">
+        <f>IF(G18=0,NA(),$D$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="45">
+        <f>IFERROR(H18-I18,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="46">
+        <f>IFERROR(IF(H18&lt;=$D$4,"OK","ALERTA"),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="22" t="inlineStr">
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>TOTAL ANUAL</t>
         </is>
       </c>
-      <c r="C19" s="23">
-        <f>SUM(C7:C18)</f>
-        <v>25500.0</v>
-      </c>
-      <c r="D19" s="23">
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="48">
         <f>SUM(D7:D18)</f>
-        <v>84500.0</v>
-      </c>
-      <c r="E19" s="24">
-        <f>IF(D19=0,"",C19/D19)</f>
-        <v>0.30177514792899407</v>
-      </c>
+        <v>15600.0</v>
+      </c>
+      <c r="E19" s="47" t="n"/>
+      <c r="F19" s="49">
+        <f>SUM(F7:F18)</f>
+        <v>15300.0</v>
+      </c>
+      <c r="G19" s="49">
+        <f>SUM(G7:G18)</f>
+        <v>48000.0</v>
+      </c>
+      <c r="H19" s="50">
+        <f>IFERROR(IF(G19=0,"",F19/G19),"")</f>
+        <v>0.31875</v>
+      </c>
+      <c r="I19" s="51" t="n"/>
+      <c r="J19" s="51" t="n"/>
+      <c r="K19" s="52" t="str">
+        <f>IFERROR(IF(H19="","",IF(H19&lt;=$D$4,"OK","ALERTA")),"")</f>
+        <v>ALERTA</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="4">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H7:I18">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>ISNA(H7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K19">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="0">
+      <formula>"ALERTA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2" stopIfTrue="0">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H19">
+    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="0">
+      <formula>AND(ISNUMBER(H7),H7&gt;$D$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
